--- a/output/Rerouting_Internal_to_DOH.xlsx
+++ b/output/Rerouting_Internal_to_DOH.xlsx
@@ -571,8 +571,10 @@
           <t>CONFIRMED (ruling)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>728918.6100000001</v>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>see monthly stock movement (Jan: 682)</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -619,8 +621,10 @@
           <t>CONFIRMED (ruling)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>5638.57</v>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>see monthly stock movement (Jan: 570)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -667,8 +671,10 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>728918.6100000001</v>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>see monthly stock movement (Jan: 2,338)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -715,8 +721,10 @@
           <t>CONFIRMED (ruling)</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>32942.25</v>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>see monthly stock movement (Jan: 52,796)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -764,7 +772,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>33803</v>
+        <v>195736.9488286315</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +819,9 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>54224.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -857,8 +867,10 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>5638.57</v>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>see monthly stock movement (Jan: 17,572)</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -905,8 +917,10 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>212405.05</v>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>see monthly stock movement (Jan: 6,169)</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -953,8 +967,10 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>96385.54000000002</v>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>see monthly stock movement (Jan: 5,583)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1001,9 +1017,7 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>3045</v>
-      </c>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1530,7 +1544,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>74728.05</v>
+        <v>21197.95</v>
       </c>
     </row>
     <row r="23">
@@ -1578,7 +1592,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>125589.17</v>
+        <v>70487.25</v>
       </c>
     </row>
     <row r="24">
@@ -1626,7 +1640,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>125589.17</v>
+        <v>70487.25</v>
       </c>
     </row>
     <row r="25">
@@ -1674,7 +1688,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1763162.330000001</v>
+        <v>181346.3900000004</v>
       </c>
     </row>
     <row r="26">
@@ -1722,7 +1736,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2394963.42</v>
+        <v>62148.42</v>
       </c>
     </row>
     <row r="27">
@@ -1770,7 +1784,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>35473.23</v>
+        <v>32231.23</v>
       </c>
     </row>
     <row r="28">
@@ -1866,7 +1880,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>125589.17</v>
+        <v>111874.02</v>
       </c>
     </row>
     <row r="30">
@@ -1914,7 +1928,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1763162.330000001</v>
+        <v>1581815.94</v>
       </c>
     </row>
     <row r="31">
@@ -2529,7 +2543,9 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
+        <v>5638.57</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2575,7 +2591,9 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="n">
+        <v>33803</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2715,7 +2733,9 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="n">
+        <v>126679.42</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2761,7 +2781,9 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="n">
+        <v>30297.55</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">

--- a/output/Rerouting_Internal_to_DOH.xlsx
+++ b/output/Rerouting_Internal_to_DOH.xlsx
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1581815.94</v>
+        <v>181346.3900000004</v>
       </c>
     </row>
     <row r="31">

--- a/output/Rerouting_Internal_to_DOH.xlsx
+++ b/output/Rerouting_Internal_to_DOH.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Head FY2025 AED (accrual)</t>
+          <t>FY2025 AED (accrual): the line where Arjun split the head, else the head total</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Indicative FY2025 AED of the line</t>
+          <t>Line detail: cash-ledger indication, or Jan 2025 from the stock movement (Feb-Dec awaited)</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>see monthly stock movement (Jan: 682)</t>
+          <t>Jan 2025 from stock movement: 682.00; Feb-Dec: awaiting the eleven monthly movement sheets</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>see monthly stock movement (Jan: 570)</t>
+          <t>Jan 2025 from stock movement: 570.00; Feb-Dec: awaiting the eleven monthly movement sheets</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>see monthly stock movement (Jan: 2,338)</t>
+          <t>Jan 2025 from stock movement: 2,338.48; Feb-Dec: awaiting the eleven monthly movement sheets</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>see monthly stock movement (Jan: 52,796)</t>
+          <t>Jan 2025 from stock movement: 52,796.00; Feb-Dec: awaiting the eleven monthly movement sheets</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>in-house dental laboratory materials</t>
+          <t>in-house CAD/CAM prosthesis materials</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Prostheses</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -758,21 +758,23 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Laboratory 100%</t>
+          <t>Prosthesis 100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>App.1 Laboratory: laboratory supplies</t>
+          <t>Ruling 13 Oct 2026: the clinic has no laboratory; prostheses made in-house (App.2 Prosthesis bucket: prothetics, implants)</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>195736.9488286315</v>
+          <t>CONFIRMED (ruling)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Jan 2025 from stock movement: 13,538.94; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -791,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>outsourced laboratory invoices</t>
+          <t>prostheses bought from external laboratories</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Prostheses</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -806,21 +808,23 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Laboratory 100%</t>
+          <t>Prosthesis 100%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>App.1 Laboratory: actual cost as billed by a provider</t>
+          <t>Ruling 13 Oct 2026: prostheses at invoiced cost (App.2 Prosthesis bucket)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>54224.25</v>
+          <t>CONFIRMED (ruling)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Jan 2025 from stock movement: 1,870.00; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -869,7 +873,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>see monthly stock movement (Jan: 17,572)</t>
+          <t>Jan 2025 from stock movement: 17,571.77; Feb-Dec: awaiting the eleven monthly movement sheets</t>
         </is>
       </c>
     </row>
@@ -919,7 +923,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>see monthly stock movement (Jan: 6,169)</t>
+          <t>Jan 2025 from stock movement: 6,169.15; Feb-Dec: awaiting the eleven monthly movement sheets</t>
         </is>
       </c>
     </row>
@@ -969,7 +973,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>see monthly stock movement (Jan: 5,583)</t>
+          <t>Jan 2025 from stock movement: 5,583.33; Feb-Dec: awaiting the eleven monthly movement sheets</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1021,11 @@
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Jan 2025 from stock movement: 1,007.80; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1026,7 +1034,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3165818.94</v>
+        <v>1817738.67</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1082,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3165818.94</v>
+        <v>324695.93</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1122,7 +1130,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3165818.94</v>
+        <v>86000</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -1146,7 +1154,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Laboratory (lab share), Dental (lab share)</t>
+          <t>Dental 100%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1170,7 +1178,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3165818.94</v>
+        <v>69820.26000000001</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1187,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>dental laboratory technicians</t>
+          <t>dental technicians (in-house prostheses)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1194,17 +1202,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Laboratory (lab share), Dental (lab share)</t>
+          <t>Prosthesis 100% (dental technicians' pool, pre-assigned on the prosthesis-coded claims)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>App.1 SWAllied incl. technicians; App.2 Laboratory includes lab staff</t>
+          <t>App.1 SWAllied incl. technicians; bucket = Prosthesis on prosthesis-coded claims (ruling 13 Oct 2026)</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>CONFIRMED (ruling)</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
@@ -1218,7 +1226,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3165818.94</v>
+        <v>182733</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -1266,7 +1274,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3165818.94</v>
+        <v>121595.5</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1314,7 +1322,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3165818.94</v>
+        <v>310000</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -1362,7 +1370,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3165818.94</v>
+        <v>110354.58</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -1410,7 +1418,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3165818.94</v>
+        <v>142881</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -1458,7 +1466,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>370348.18</v>
+        <v>351150.23</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -1506,7 +1514,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>370348.18</v>
+        <v>19197.95</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -1554,7 +1562,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>253569.45475</v>
+        <v>34009.68</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -1602,7 +1610,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>253569.45475</v>
+        <v>34349.57</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1650,7 +1658,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>253569.45475</v>
+        <v>145165.3229166667</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1706,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>253569.45475</v>
+        <v>9133.031833333331</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -1746,7 +1754,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>253569.45475</v>
+        <v>30911.85</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -1794,7 +1802,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>253569.45475</v>
+        <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -1890,7 +1898,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>889431.99</v>
+        <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -1938,7 +1946,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>889431.99</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -1986,7 +1994,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>889431.99</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -2126,7 +2134,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>50409.285</v>
+        <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -2563,12 +2571,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>outsourced laboratory work</t>
+          <t>prostheses bought from external laboratories</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Prostheses</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2578,17 +2586,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Laboratory 100%</t>
+          <t>Prosthesis 100%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>App.1 Laboratory: actual cost as billed</t>
+          <t>Ruling 13 Oct 2026: prostheses at invoiced cost (App.2 Prosthesis bucket)</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>CONFIRMED (ruling)</t>
         </is>
       </c>
       <c r="J44" s="3" t="n">

--- a/output/Rerouting_Internal_to_DOH.xlsx
+++ b/output/Rerouting_Internal_to_DOH.xlsx
@@ -1624,17 +1624,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>SWDoc / SWNurs (on-cost)</t>
+          <t>on-cost: salary share → SWDoc / SWNurs / SWAllied / OHF</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Anaesthesia 2%, Dental 98%</t>
+          <t>follows the staff category</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1642,9 +1642,9 @@
           <t>App.1 Cost of Labour: salaries, wages and on-costs follow the staff category</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>NEEDS GL DETAIL</t>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED (ruling 13 Oct 2026: salary share by staff category, employees only)</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>on-cost by staff category (SWDoc / SWNurs / SWAllied / OHF)</t>
+          <t>on-cost: salary share → SWDoc / SWNurs / SWAllied / OHF</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1690,9 +1690,9 @@
           <t>App.1 Cost of Labour: on-costs</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>NEEDS GL DETAIL</t>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED (ruling 13 Oct 2026: salary share by staff category, employees only)</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>on-cost by staff category (SWDoc / SWNurs / SWAllied / OHF)</t>
+          <t>on-cost: salary share → SWDoc / SWNurs / SWAllied / OHF</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1882,9 +1882,9 @@
           <t>App.1 Cost of Labour: on-costs follow the staff category</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>NEEDS GL DETAIL</t>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED (ruling 13 Oct 2026: salary share by staff category, employees only)</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>on-cost by staff category (SWDoc / SWNurs / SWAllied / OHF)</t>
+          <t>on-cost: salary share → SWDoc / SWNurs / SWAllied / OHF</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2120,9 +2120,9 @@
           <t>App.1 Cost of Labour: on-costs</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>INFERRED (Insurance Exp sheet)</t>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED (ruling 13 Oct 2026: salary share by staff category, employees only)</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>

--- a/output/Rerouting_Internal_to_DOH.xlsx
+++ b/output/Rerouting_Internal_to_DOH.xlsx
@@ -1624,12 +1624,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>on-cost: salary share → SWDoc / SWNurs / SWAllied / OHF</t>
+          <t>on-cost → SWDoc / SWNurs by licensed headcount</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED (ruling 13 Oct 2026: salary share by staff category, employees only)</t>
+          <t>CONFIRMED (ruling 13 Oct 2026: Option 3, by the nature of the cost)</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>on-cost: salary share → SWDoc / SWNurs / SWAllied / OHF</t>
+          <t>on-cost → SWDoc / SWNurs / SWAllied / OHF by headcount</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED (ruling 13 Oct 2026: salary share by staff category, employees only)</t>
+          <t>CONFIRMED (ruling 13 Oct 2026: Option 3, by the nature of the cost)</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>on-cost: salary share → SWDoc / SWNurs / SWAllied / OHF</t>
+          <t>on-cost → SWDoc / SWNurs / SWAllied / OHF by salary share</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED (ruling 13 Oct 2026: salary share by staff category, employees only)</t>
+          <t>CONFIRMED (ruling 13 Oct 2026: Option 3, by the nature of the cost)</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>on-cost: salary share → SWDoc / SWNurs / SWAllied / OHF</t>
+          <t>on-cost → SWDoc / SWNurs / SWAllied / OHF by headcount</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED (ruling 13 Oct 2026: salary share by staff category, employees only)</t>
+          <t>CONFIRMED (ruling 13 Oct 2026: Option 3, by the nature of the cost)</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>

--- a/output/Rerouting_Internal_to_DOH.xlsx
+++ b/output/Rerouting_Internal_to_DOH.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>7163.174999999999</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 682.00; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>7718.816666666667</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 570.00; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>26103.94878333332</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 2,338.48; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>441488.8863636373</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 52,796.00; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>189441.8683119649</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 13,538.94; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>54224.25</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 1,870.00; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>Consumption sheet External LAB (cash in hand), twelve months</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>205910.0414666665</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 17,571.77; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price; includes the August residual 431.82 placed on MS (ruling)</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>69270.0524249999</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 6,169.15; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>21981.94666666666</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 5,583.33; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1040318.250896056</v>
+        <v>17015.2614</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Jan 2025 from stock movement: 1,007.80; Feb-Dec: awaiting the eleven monthly movement sheets</t>
+          <t>twelve stock-movement sheets, usage net of returns: Jan-Apr transaction value, May-Nov supplier price, Dec buying price</t>
         </is>
       </c>
     </row>
